--- a/exemplaires-import-biens/exemplaires-import-biens/exemplaire_blocs_immeubles.xlsx
+++ b/exemplaires-import-biens/exemplaires-import-biens/exemplaire_blocs_immeubles.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1B7579-BD52-43D5-94C9-5F773D1674EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8616"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -141,19 +142,19 @@
     <t xml:space="preserve">1er etage </t>
   </si>
   <si>
-    <t>B_1</t>
-  </si>
-  <si>
-    <t>B_2</t>
-  </si>
-  <si>
-    <t>B_3</t>
+    <t>AB1</t>
+  </si>
+  <si>
+    <t>AB2</t>
+  </si>
+  <si>
+    <t>AB3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -568,38 +569,38 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AE8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" customWidth="1"/>
+    <col min="3" max="3" width="8.90625" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="22.88671875" customWidth="1"/>
-    <col min="8" max="8" width="21.77734375" customWidth="1"/>
-    <col min="9" max="9" width="23.33203125" customWidth="1"/>
+    <col min="7" max="7" width="22.90625" customWidth="1"/>
+    <col min="8" max="8" width="21.81640625" customWidth="1"/>
+    <col min="9" max="9" width="23.36328125" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="12.77734375" customWidth="1"/>
+    <col min="12" max="12" width="12.81640625" customWidth="1"/>
     <col min="13" max="13" width="19" customWidth="1"/>
-    <col min="14" max="14" width="19.21875" customWidth="1"/>
-    <col min="15" max="15" width="17.5546875" customWidth="1"/>
-    <col min="16" max="16" width="16.21875" customWidth="1"/>
-    <col min="17" max="17" width="14.21875" customWidth="1"/>
-    <col min="18" max="18" width="12.109375" customWidth="1"/>
-    <col min="19" max="19" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.1796875" customWidth="1"/>
+    <col min="15" max="15" width="17.54296875" customWidth="1"/>
+    <col min="16" max="16" width="16.1796875" customWidth="1"/>
+    <col min="17" max="17" width="14.1796875" customWidth="1"/>
+    <col min="18" max="18" width="12.08984375" customWidth="1"/>
+    <col min="19" max="19" width="15.08984375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
-    <col min="21" max="21" width="18.5546875" customWidth="1"/>
+    <col min="21" max="21" width="18.54296875" customWidth="1"/>
     <col min="22" max="22" width="19" customWidth="1"/>
-    <col min="23" max="24" width="17.88671875" customWidth="1"/>
+    <col min="23" max="24" width="17.90625" customWidth="1"/>
     <col min="25" max="26" width="19" customWidth="1"/>
-    <col min="27" max="29" width="17.88671875" customWidth="1"/>
+    <col min="27" max="29" width="17.90625" customWidth="1"/>
     <col min="30" max="30" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -694,7 +695,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>35</v>
       </c>
@@ -742,7 +743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>35</v>
       </c>
@@ -793,7 +794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>35</v>
       </c>
@@ -843,6 +844,18 @@
       <c r="V4">
         <v>2</v>
       </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="D7" s="7"/>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="D8" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
